--- a/data/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/data/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="766" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35048B3F-52C8-454F-901C-148416F4CF30}"/>
+  <xr:revisionPtr revIDLastSave="767" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E594027-CE49-4F92-8FC3-E5902BADAED8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="99">
   <si>
     <t>Fecha</t>
   </si>
@@ -3039,7 +3039,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R627"/>
+  <dimension ref="A1:R636"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -12016,7 +12016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>46247</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>46247</v>
       </c>
@@ -12044,8 +12044,153 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A627" s="1"/>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A627" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1</v>
+      </c>
+      <c r="C627" t="s">
+        <v>47</v>
+      </c>
+      <c r="D627">
+        <v>1</v>
+      </c>
+      <c r="E627">
+        <f>SUM(D627:D631)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1</v>
+      </c>
+      <c r="C628" t="s">
+        <v>48</v>
+      </c>
+      <c r="D628">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A629" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1</v>
+      </c>
+      <c r="C629" t="s">
+        <v>20</v>
+      </c>
+      <c r="D629">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A630" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1</v>
+      </c>
+      <c r="C630" t="s">
+        <v>28</v>
+      </c>
+      <c r="D630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A631" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1</v>
+      </c>
+      <c r="C631" t="s">
+        <v>10</v>
+      </c>
+      <c r="D631">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A632" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B632" t="s">
+        <v>17</v>
+      </c>
+      <c r="C632" t="s">
+        <v>51</v>
+      </c>
+      <c r="D632">
+        <v>1</v>
+      </c>
+      <c r="E632">
+        <f>SUM(D632:D636)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A633" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B633" t="s">
+        <v>17</v>
+      </c>
+      <c r="C633" t="s">
+        <v>9</v>
+      </c>
+      <c r="D633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A634" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B634" t="s">
+        <v>17</v>
+      </c>
+      <c r="C634" t="s">
+        <v>69</v>
+      </c>
+      <c r="D634">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A635" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B635" t="s">
+        <v>17</v>
+      </c>
+      <c r="C635" t="s">
+        <v>71</v>
+      </c>
+      <c r="D635">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A636" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B636" t="s">
+        <v>17</v>
+      </c>
+      <c r="C636" t="s">
+        <v>45</v>
+      </c>
+      <c r="D636">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D596" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/data/Base Futbol Jueves del Cordero Susurrador.xlsx
+++ b/data/Base Futbol Jueves del Cordero Susurrador.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb38a873320e33ce/Documents/GitHub/JuevesdelCorderoSusurrador/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="767" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E594027-CE49-4F92-8FC3-E5902BADAED8}"/>
+  <xr:revisionPtr revIDLastSave="768" documentId="11_F02E00BCE8A8F848497B2C5B9963098BB27E3D04" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4B594D8-26BC-45BF-B10C-C44019E099FD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="100">
   <si>
     <t>Fecha</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>Maxi Pintureria</t>
+  </si>
+  <si>
+    <t>Agustin (amigo Bigo)</t>
   </si>
 </sst>
 </file>
@@ -3039,7 +3042,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R636"/>
+  <dimension ref="A1:R646"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -12190,6 +12193,154 @@
       </c>
       <c r="D636">
         <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A637" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1</v>
+      </c>
+      <c r="C637" t="s">
+        <v>9</v>
+      </c>
+      <c r="D637">
+        <v>2</v>
+      </c>
+      <c r="E637">
+        <f>SUM(D637:D641)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A638" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1</v>
+      </c>
+      <c r="C638" t="s">
+        <v>10</v>
+      </c>
+      <c r="D638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A639" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1</v>
+      </c>
+      <c r="C639" t="s">
+        <v>47</v>
+      </c>
+      <c r="D639">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A640" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1</v>
+      </c>
+      <c r="C640" t="s">
+        <v>71</v>
+      </c>
+      <c r="D640">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A641" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1</v>
+      </c>
+      <c r="C641" t="s">
+        <v>76</v>
+      </c>
+      <c r="D641">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A642" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B642" t="s">
+        <v>17</v>
+      </c>
+      <c r="C642" t="s">
+        <v>70</v>
+      </c>
+      <c r="D642">
+        <v>0</v>
+      </c>
+      <c r="E642">
+        <f>SUM(D642:D646)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A643" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B643" t="s">
+        <v>17</v>
+      </c>
+      <c r="C643" t="s">
+        <v>99</v>
+      </c>
+      <c r="D643">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A644" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B644" t="s">
+        <v>17</v>
+      </c>
+      <c r="C644" t="s">
+        <v>45</v>
+      </c>
+      <c r="D644">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A645" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B645" t="s">
+        <v>17</v>
+      </c>
+      <c r="C645" t="s">
+        <v>30</v>
+      </c>
+      <c r="D645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A646" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B646" t="s">
+        <v>17</v>
+      </c>
+      <c r="C646" t="s">
+        <v>16</v>
+      </c>
+      <c r="D646">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
